--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
   <si>
     <t>Value Set (all codes)</t>
@@ -423,52 +426,54 @@
       <c r="A16" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -483,63 +488,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-AtElgaEmedCodeSystemPlaneintragStatusReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
